--- a/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -717,16 +717,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1639700</v>
+        <v>1635200</v>
       </c>
       <c r="E8" s="3">
-        <v>2067500</v>
+        <v>2061900</v>
       </c>
       <c r="F8" s="3">
-        <v>1951100</v>
+        <v>1945800</v>
       </c>
       <c r="G8" s="3">
-        <v>2875600</v>
+        <v>2867700</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -749,16 +749,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1092300</v>
+        <v>1089300</v>
       </c>
       <c r="E9" s="3">
-        <v>1430300</v>
+        <v>1426400</v>
       </c>
       <c r="F9" s="3">
-        <v>1430600</v>
+        <v>1426700</v>
       </c>
       <c r="G9" s="3">
-        <v>1792500</v>
+        <v>1787600</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>547400</v>
+        <v>545900</v>
       </c>
       <c r="E10" s="3">
-        <v>637200</v>
+        <v>635400</v>
       </c>
       <c r="F10" s="3">
-        <v>520500</v>
+        <v>519100</v>
       </c>
       <c r="G10" s="3">
-        <v>1083100</v>
+        <v>1080100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -891,16 +891,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-32700</v>
+        <v>-32600</v>
       </c>
       <c r="E14" s="3">
-        <v>31000</v>
+        <v>30900</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-164100</v>
+        <v>-163700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -966,16 +966,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1171900</v>
+        <v>1168700</v>
       </c>
       <c r="E17" s="3">
-        <v>1559900</v>
+        <v>1555600</v>
       </c>
       <c r="F17" s="3">
-        <v>1568300</v>
+        <v>1564000</v>
       </c>
       <c r="G17" s="3">
-        <v>2153600</v>
+        <v>2147800</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -998,16 +998,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>467800</v>
+        <v>466500</v>
       </c>
       <c r="E18" s="3">
-        <v>507600</v>
+        <v>506200</v>
       </c>
       <c r="F18" s="3">
-        <v>382800</v>
+        <v>381700</v>
       </c>
       <c r="G18" s="3">
-        <v>721900</v>
+        <v>720000</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1044,16 +1044,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-91300</v>
+        <v>-91100</v>
       </c>
       <c r="E20" s="3">
-        <v>-120100</v>
+        <v>-119700</v>
       </c>
       <c r="F20" s="3">
-        <v>-62200</v>
+        <v>-62100</v>
       </c>
       <c r="G20" s="3">
-        <v>-70700</v>
+        <v>-70600</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1076,13 +1076,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>486300</v>
+        <v>485000</v>
       </c>
       <c r="E21" s="3">
-        <v>403900</v>
+        <v>402800</v>
       </c>
       <c r="F21" s="3">
-        <v>408900</v>
+        <v>407800</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1117,7 +1117,7 @@
         <v>900</v>
       </c>
       <c r="G22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1140,16 +1140,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>375700</v>
+        <v>374600</v>
       </c>
       <c r="E23" s="3">
-        <v>386800</v>
+        <v>385800</v>
       </c>
       <c r="F23" s="3">
-        <v>319600</v>
+        <v>318800</v>
       </c>
       <c r="G23" s="3">
-        <v>650300</v>
+        <v>648600</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1172,16 +1172,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>139300</v>
+        <v>138900</v>
       </c>
       <c r="E24" s="3">
-        <v>151100</v>
+        <v>150700</v>
       </c>
       <c r="F24" s="3">
-        <v>128500</v>
+        <v>128200</v>
       </c>
       <c r="G24" s="3">
-        <v>524700</v>
+        <v>523300</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1236,16 +1236,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>236400</v>
+        <v>235700</v>
       </c>
       <c r="E26" s="3">
-        <v>235700</v>
+        <v>235100</v>
       </c>
       <c r="F26" s="3">
-        <v>191100</v>
+        <v>190600</v>
       </c>
       <c r="G26" s="3">
-        <v>125600</v>
+        <v>125300</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1268,16 +1268,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>176400</v>
+        <v>175900</v>
       </c>
       <c r="E27" s="3">
-        <v>155100</v>
+        <v>154700</v>
       </c>
       <c r="F27" s="3">
-        <v>141500</v>
+        <v>141100</v>
       </c>
       <c r="G27" s="3">
-        <v>206900</v>
+        <v>206300</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1428,16 +1428,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>91300</v>
+        <v>91100</v>
       </c>
       <c r="E32" s="3">
-        <v>120100</v>
+        <v>119700</v>
       </c>
       <c r="F32" s="3">
-        <v>62200</v>
+        <v>62100</v>
       </c>
       <c r="G32" s="3">
-        <v>70700</v>
+        <v>70600</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1460,16 +1460,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>176400</v>
+        <v>175900</v>
       </c>
       <c r="E33" s="3">
-        <v>155100</v>
+        <v>154700</v>
       </c>
       <c r="F33" s="3">
-        <v>141500</v>
+        <v>141100</v>
       </c>
       <c r="G33" s="3">
-        <v>206900</v>
+        <v>206300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1524,16 +1524,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>176400</v>
+        <v>175900</v>
       </c>
       <c r="E35" s="3">
-        <v>155100</v>
+        <v>154700</v>
       </c>
       <c r="F35" s="3">
-        <v>141500</v>
+        <v>141100</v>
       </c>
       <c r="G35" s="3">
-        <v>206900</v>
+        <v>206300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1621,10 +1621,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3587400</v>
+        <v>3577600</v>
       </c>
       <c r="E41" s="3">
-        <v>3700900</v>
+        <v>3690800</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1653,10 +1653,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>92800</v>
+        <v>92600</v>
       </c>
       <c r="E42" s="3">
-        <v>264400</v>
+        <v>263600</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1685,10 +1685,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1637500</v>
+        <v>1633000</v>
       </c>
       <c r="E43" s="3">
-        <v>1589500</v>
+        <v>1585200</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1717,10 +1717,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4683100</v>
+        <v>4670300</v>
       </c>
       <c r="E44" s="3">
-        <v>5213100</v>
+        <v>5198900</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1749,10 +1749,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>171000</v>
+        <v>170500</v>
       </c>
       <c r="E45" s="3">
-        <v>1229000</v>
+        <v>1225600</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1781,10 +1781,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10171800</v>
+        <v>10144000</v>
       </c>
       <c r="E46" s="3">
-        <v>11996900</v>
+        <v>11964100</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1813,10 +1813,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5662900</v>
+        <v>5647500</v>
       </c>
       <c r="E47" s="3">
-        <v>5820600</v>
+        <v>5804700</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1845,10 +1845,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5212800</v>
+        <v>5198600</v>
       </c>
       <c r="E48" s="3">
-        <v>5205200</v>
+        <v>5191000</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1877,10 +1877,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1791600</v>
+        <v>1786700</v>
       </c>
       <c r="E49" s="3">
-        <v>1817800</v>
+        <v>1812800</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1976,7 +1976,7 @@
         <v>22100</v>
       </c>
       <c r="E52" s="3">
-        <v>19900</v>
+        <v>19800</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2037,10 +2037,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22861300</v>
+        <v>22798900</v>
       </c>
       <c r="E54" s="3">
-        <v>24860400</v>
+        <v>24792500</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2097,10 +2097,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2184600</v>
+        <v>2178600</v>
       </c>
       <c r="E57" s="3">
-        <v>2499100</v>
+        <v>2492300</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2129,10 +2129,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2091300</v>
+        <v>2085600</v>
       </c>
       <c r="E58" s="3">
-        <v>2305900</v>
+        <v>2299600</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2161,10 +2161,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2466800</v>
+        <v>2460100</v>
       </c>
       <c r="E59" s="3">
-        <v>3578100</v>
+        <v>3568300</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2193,10 +2193,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6742700</v>
+        <v>6724300</v>
       </c>
       <c r="E60" s="3">
-        <v>8383100</v>
+        <v>8360200</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2225,10 +2225,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5300300</v>
+        <v>5285800</v>
       </c>
       <c r="E61" s="3">
-        <v>5249800</v>
+        <v>5235500</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1309200</v>
+        <v>1305700</v>
       </c>
       <c r="E62" s="3">
-        <v>1383300</v>
+        <v>1379500</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2385,10 +2385,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17150600</v>
+        <v>17103800</v>
       </c>
       <c r="E66" s="3">
-        <v>19024600</v>
+        <v>18972700</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2559,10 +2559,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4167200</v>
+        <v>4155800</v>
       </c>
       <c r="E72" s="3">
-        <v>4066200</v>
+        <v>4055100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2687,10 +2687,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5710700</v>
+        <v>5695100</v>
       </c>
       <c r="E76" s="3">
-        <v>5835700</v>
+        <v>5819800</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2788,16 +2788,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>176400</v>
+        <v>175900</v>
       </c>
       <c r="E81" s="3">
-        <v>155100</v>
+        <v>154700</v>
       </c>
       <c r="F81" s="3">
-        <v>141500</v>
+        <v>141100</v>
       </c>
       <c r="G81" s="3">
-        <v>206900</v>
+        <v>206300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -3026,13 +3026,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>231700</v>
+        <v>231100</v>
       </c>
       <c r="E89" s="3">
-        <v>1101000</v>
+        <v>1098000</v>
       </c>
       <c r="F89" s="3">
-        <v>-1033500</v>
+        <v>-1030700</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -3168,13 +3168,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>49200</v>
+        <v>49000</v>
       </c>
       <c r="E94" s="3">
-        <v>-425900</v>
+        <v>-424800</v>
       </c>
       <c r="F94" s="3">
-        <v>32300</v>
+        <v>32200</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3214,13 +3214,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-67000</v>
+        <v>-66800</v>
       </c>
       <c r="E96" s="3">
-        <v>-91900</v>
+        <v>-91700</v>
       </c>
       <c r="F96" s="3">
-        <v>-41900</v>
+        <v>-41800</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3342,13 +3342,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-233800</v>
+        <v>-233100</v>
       </c>
       <c r="E100" s="3">
-        <v>-1265300</v>
+        <v>-1261900</v>
       </c>
       <c r="F100" s="3">
-        <v>680700</v>
+        <v>678800</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3374,13 +3374,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-160600</v>
+        <v>-160200</v>
       </c>
       <c r="E101" s="3">
-        <v>-39900</v>
+        <v>-39800</v>
       </c>
       <c r="F101" s="3">
-        <v>-238900</v>
+        <v>-238200</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3406,13 +3406,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-113500</v>
+        <v>-113200</v>
       </c>
       <c r="E102" s="3">
-        <v>-630200</v>
+        <v>-628400</v>
       </c>
       <c r="F102" s="3">
-        <v>-559400</v>
+        <v>-557900</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>SGHIY</t>
   </si>
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
-        <v>44561</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,22 +711,25 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1635200</v>
+        <v>2549100</v>
       </c>
       <c r="E8" s="3">
-        <v>2061900</v>
+        <v>1637900</v>
       </c>
       <c r="F8" s="3">
-        <v>1945800</v>
+        <v>2065200</v>
       </c>
       <c r="G8" s="3">
-        <v>2867700</v>
+        <v>1948900</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -743,22 +746,25 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1089300</v>
+        <v>1458100</v>
       </c>
       <c r="E9" s="3">
-        <v>1426400</v>
+        <v>1091100</v>
       </c>
       <c r="F9" s="3">
-        <v>1426700</v>
+        <v>1428800</v>
       </c>
       <c r="G9" s="3">
-        <v>1787600</v>
+        <v>1429000</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -775,22 +781,25 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>545900</v>
+        <v>1090900</v>
       </c>
       <c r="E10" s="3">
-        <v>635400</v>
+        <v>546800</v>
       </c>
       <c r="F10" s="3">
-        <v>519100</v>
+        <v>636500</v>
       </c>
       <c r="G10" s="3">
-        <v>1080100</v>
+        <v>519900</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -807,8 +816,11 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,8 +833,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -853,8 +866,11 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,22 +901,25 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-32600</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>30900</v>
+        <v>-32700</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="G14" s="3">
-        <v>-163700</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -917,8 +936,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -949,8 +971,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,22 +985,23 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1168700</v>
+        <v>1697900</v>
       </c>
       <c r="E17" s="3">
-        <v>1555600</v>
+        <v>1170700</v>
       </c>
       <c r="F17" s="3">
-        <v>1564000</v>
+        <v>1558200</v>
       </c>
       <c r="G17" s="3">
-        <v>2147800</v>
+        <v>1566600</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -992,22 +1018,25 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>466500</v>
+        <v>851100</v>
       </c>
       <c r="E18" s="3">
-        <v>506200</v>
+        <v>467300</v>
       </c>
       <c r="F18" s="3">
-        <v>381700</v>
+        <v>507100</v>
       </c>
       <c r="G18" s="3">
-        <v>720000</v>
+        <v>382400</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1024,8 +1053,11 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,22 +1070,23 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-91100</v>
+        <v>-106500</v>
       </c>
       <c r="E20" s="3">
-        <v>-119700</v>
+        <v>-91200</v>
       </c>
       <c r="F20" s="3">
-        <v>-62100</v>
+        <v>-119900</v>
       </c>
       <c r="G20" s="3">
-        <v>-70600</v>
+        <v>-62200</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1070,22 +1103,25 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>485000</v>
+        <v>741800</v>
       </c>
       <c r="E21" s="3">
-        <v>402800</v>
+        <v>485800</v>
       </c>
       <c r="F21" s="3">
-        <v>407800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>403500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>408400</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1102,23 +1138,26 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
-        <v>800</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1134,22 +1173,25 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>374600</v>
+        <v>744000</v>
       </c>
       <c r="E23" s="3">
-        <v>385800</v>
+        <v>375300</v>
       </c>
       <c r="F23" s="3">
-        <v>318800</v>
+        <v>386400</v>
       </c>
       <c r="G23" s="3">
-        <v>648600</v>
+        <v>319300</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1166,22 +1208,25 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>138900</v>
+        <v>400600</v>
       </c>
       <c r="E24" s="3">
-        <v>150700</v>
+        <v>139100</v>
       </c>
       <c r="F24" s="3">
-        <v>128200</v>
+        <v>150900</v>
       </c>
       <c r="G24" s="3">
-        <v>523300</v>
+        <v>128400</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1198,8 +1243,11 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,22 +1278,25 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>235700</v>
+        <v>343400</v>
       </c>
       <c r="E26" s="3">
-        <v>235100</v>
+        <v>236100</v>
       </c>
       <c r="F26" s="3">
-        <v>190600</v>
+        <v>235500</v>
       </c>
       <c r="G26" s="3">
-        <v>125300</v>
+        <v>190900</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1262,22 +1313,25 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>175900</v>
+        <v>262200</v>
       </c>
       <c r="E27" s="3">
-        <v>154700</v>
+        <v>176200</v>
       </c>
       <c r="F27" s="3">
-        <v>141100</v>
+        <v>155000</v>
       </c>
       <c r="G27" s="3">
-        <v>206300</v>
+        <v>141300</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1294,8 +1348,11 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1383,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1418,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1453,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,22 +1488,25 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>91100</v>
+        <v>106500</v>
       </c>
       <c r="E32" s="3">
-        <v>119700</v>
+        <v>91200</v>
       </c>
       <c r="F32" s="3">
-        <v>62100</v>
+        <v>119900</v>
       </c>
       <c r="G32" s="3">
-        <v>70600</v>
+        <v>62200</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1454,22 +1523,25 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>175900</v>
+        <v>262200</v>
       </c>
       <c r="E33" s="3">
-        <v>154700</v>
+        <v>176200</v>
       </c>
       <c r="F33" s="3">
-        <v>141100</v>
+        <v>155000</v>
       </c>
       <c r="G33" s="3">
-        <v>206300</v>
+        <v>141300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1486,8 +1558,11 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,22 +1593,25 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>175900</v>
+        <v>262200</v>
       </c>
       <c r="E35" s="3">
-        <v>154700</v>
+        <v>176200</v>
       </c>
       <c r="F35" s="3">
-        <v>141100</v>
+        <v>155000</v>
       </c>
       <c r="G35" s="3">
-        <v>206300</v>
+        <v>141300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1550,28 +1628,31 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
-        <v>44561</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1587,8 +1668,11 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1685,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,19 +1700,20 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3577600</v>
+        <v>3230100</v>
       </c>
       <c r="E41" s="3">
-        <v>3690800</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+        <v>3583400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3696800</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1647,19 +1733,22 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>92600</v>
+        <v>336200</v>
       </c>
       <c r="E42" s="3">
-        <v>263600</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>92700</v>
+      </c>
+      <c r="F42" s="3">
+        <v>264100</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1679,19 +1768,22 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1633000</v>
+        <v>1575000</v>
       </c>
       <c r="E43" s="3">
-        <v>1585200</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+        <v>1635700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1587800</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1711,19 +1803,22 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4670300</v>
+        <v>4341900</v>
       </c>
       <c r="E44" s="3">
-        <v>5198900</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
+        <v>4678000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>5207400</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1743,19 +1838,22 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>170500</v>
+        <v>142000</v>
       </c>
       <c r="E45" s="3">
-        <v>1225600</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+        <v>170800</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1227700</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1775,19 +1873,22 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10144000</v>
+        <v>9625100</v>
       </c>
       <c r="E46" s="3">
-        <v>11964100</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>10160700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11983800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1807,19 +1908,22 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5647500</v>
+        <v>5811300</v>
       </c>
       <c r="E47" s="3">
-        <v>5804700</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+        <v>5656800</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5814200</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1839,19 +1943,22 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5198600</v>
+        <v>5601000</v>
       </c>
       <c r="E48" s="3">
-        <v>5191000</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>5207100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5199500</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1871,19 +1978,22 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1786700</v>
+        <v>1898100</v>
       </c>
       <c r="E49" s="3">
-        <v>1812800</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+        <v>1789700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1815800</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1903,8 +2013,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2048,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,19 +2083,22 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E52" s="3">
         <v>22100</v>
       </c>
-      <c r="E52" s="3">
-        <v>19800</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>19900</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -1999,8 +2118,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,19 +2153,22 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22798900</v>
+        <v>22960900</v>
       </c>
       <c r="E54" s="3">
-        <v>24792500</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>22836300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>24833200</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2063,8 +2188,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2205,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,19 +2220,20 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2178600</v>
+        <v>2440300</v>
       </c>
       <c r="E57" s="3">
-        <v>2492300</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>2182200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2496400</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2123,19 +2253,22 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2085600</v>
+        <v>1869600</v>
       </c>
       <c r="E58" s="3">
-        <v>2299600</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>2089000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2303400</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2155,19 +2288,22 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2460100</v>
+        <v>1762800</v>
       </c>
       <c r="E59" s="3">
-        <v>3568300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>2464100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3574200</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2187,19 +2323,22 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6724300</v>
+        <v>6072700</v>
       </c>
       <c r="E60" s="3">
-        <v>8360200</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>6735300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>8373900</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2219,19 +2358,22 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5285800</v>
+        <v>5663400</v>
       </c>
       <c r="E61" s="3">
-        <v>5235500</v>
+        <v>5294500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>5244100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2251,19 +2393,22 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1305700</v>
+        <v>1305900</v>
       </c>
       <c r="E62" s="3">
-        <v>1379500</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>1307800</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1381700</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2283,8 +2428,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2463,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2498,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,19 +2533,22 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17103800</v>
+        <v>16993300</v>
       </c>
       <c r="E66" s="3">
-        <v>18972700</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>17131900</v>
+      </c>
+      <c r="F66" s="3">
+        <v>19003900</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2411,8 +2568,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2585,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2618,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2653,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2688,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,19 +2723,22 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4155800</v>
+        <v>4370600</v>
       </c>
       <c r="E72" s="3">
-        <v>4055100</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>4162700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4061700</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2585,8 +2758,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2793,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2828,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,19 +2863,22 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5695100</v>
+        <v>5967500</v>
       </c>
       <c r="E76" s="3">
-        <v>5819800</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>5704400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>5829400</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2713,8 +2898,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,28 +2933,31 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
-        <v>44561</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2782,22 +2973,25 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>175900</v>
+        <v>262200</v>
       </c>
       <c r="E81" s="3">
-        <v>154700</v>
+        <v>176200</v>
       </c>
       <c r="F81" s="3">
-        <v>141100</v>
+        <v>155000</v>
       </c>
       <c r="G81" s="3">
-        <v>206300</v>
+        <v>141300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2814,8 +3008,11 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,8 +3025,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2860,8 +3058,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3093,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3128,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3163,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3198,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,22 +3233,25 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>231100</v>
+        <v>326200</v>
       </c>
       <c r="E89" s="3">
-        <v>1098000</v>
+        <v>231500</v>
       </c>
       <c r="F89" s="3">
-        <v>-1030700</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>1099800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1032400</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3052,8 +3268,11 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,20 +3285,21 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3262900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-157900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-208400</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -3098,8 +3318,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3353,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,22 +3388,25 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>49000</v>
+        <v>-566100</v>
       </c>
       <c r="E94" s="3">
-        <v>-424800</v>
+        <v>49100</v>
       </c>
       <c r="F94" s="3">
-        <v>32200</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-425500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>32300</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3194,8 +3423,11 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,23 +3440,24 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-66800</v>
+        <v>-61200</v>
       </c>
       <c r="E96" s="3">
-        <v>-91700</v>
+        <v>-66900</v>
       </c>
       <c r="F96" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="G96" s="3">
         <v>-41800</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3240,8 +3473,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3508,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3543,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,22 +3578,25 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-233100</v>
+        <v>-194600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1261900</v>
+        <v>-233500</v>
       </c>
       <c r="F100" s="3">
-        <v>678800</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>-1263900</v>
+      </c>
+      <c r="G100" s="3">
+        <v>679900</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3368,22 +3613,25 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-160200</v>
+        <v>81100</v>
       </c>
       <c r="E101" s="3">
-        <v>-39800</v>
+        <v>-160500</v>
       </c>
       <c r="F101" s="3">
-        <v>-238200</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+        <v>-39900</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-238600</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3400,22 +3648,25 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-113200</v>
+        <v>-353400</v>
       </c>
       <c r="E102" s="3">
-        <v>-628400</v>
+        <v>-113400</v>
       </c>
       <c r="F102" s="3">
-        <v>-557900</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>-629500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-558800</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3430,6 +3681,9 @@
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>SGHIY</t>
   </si>
@@ -720,16 +720,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2549100</v>
+        <v>2552600</v>
       </c>
       <c r="E8" s="3">
-        <v>1637900</v>
+        <v>1640200</v>
       </c>
       <c r="F8" s="3">
-        <v>2065200</v>
+        <v>2068100</v>
       </c>
       <c r="G8" s="3">
-        <v>1948900</v>
+        <v>1951700</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -755,16 +755,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1458100</v>
+        <v>1460200</v>
       </c>
       <c r="E9" s="3">
-        <v>1091100</v>
+        <v>1092700</v>
       </c>
       <c r="F9" s="3">
-        <v>1428800</v>
+        <v>1430800</v>
       </c>
       <c r="G9" s="3">
-        <v>1429000</v>
+        <v>1431000</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -790,16 +790,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1090900</v>
+        <v>1092500</v>
       </c>
       <c r="E10" s="3">
-        <v>546800</v>
+        <v>547500</v>
       </c>
       <c r="F10" s="3">
-        <v>636500</v>
+        <v>637400</v>
       </c>
       <c r="G10" s="3">
-        <v>519900</v>
+        <v>520600</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -992,16 +992,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1697900</v>
+        <v>1700300</v>
       </c>
       <c r="E17" s="3">
-        <v>1170700</v>
+        <v>1172300</v>
       </c>
       <c r="F17" s="3">
-        <v>1558200</v>
+        <v>1560400</v>
       </c>
       <c r="G17" s="3">
-        <v>1566600</v>
+        <v>1568800</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1027,16 +1027,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>851100</v>
+        <v>852300</v>
       </c>
       <c r="E18" s="3">
-        <v>467300</v>
+        <v>467900</v>
       </c>
       <c r="F18" s="3">
-        <v>507100</v>
+        <v>507800</v>
       </c>
       <c r="G18" s="3">
-        <v>382400</v>
+        <v>382900</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1077,16 +1077,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-106500</v>
+        <v>-106700</v>
       </c>
       <c r="E20" s="3">
-        <v>-91200</v>
+        <v>-91400</v>
       </c>
       <c r="F20" s="3">
-        <v>-119900</v>
+        <v>-120100</v>
       </c>
       <c r="G20" s="3">
-        <v>-62200</v>
+        <v>-62300</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1112,16 +1112,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>741800</v>
+        <v>742800</v>
       </c>
       <c r="E21" s="3">
-        <v>485800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>403500</v>
+        <v>486400</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G21" s="3">
-        <v>408400</v>
+        <v>409000</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1182,16 +1182,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>744000</v>
+        <v>745000</v>
       </c>
       <c r="E23" s="3">
-        <v>375300</v>
+        <v>375800</v>
       </c>
       <c r="F23" s="3">
-        <v>386400</v>
+        <v>386900</v>
       </c>
       <c r="G23" s="3">
-        <v>319300</v>
+        <v>319700</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1217,16 +1217,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>400600</v>
+        <v>401100</v>
       </c>
       <c r="E24" s="3">
-        <v>139100</v>
+        <v>139300</v>
       </c>
       <c r="F24" s="3">
-        <v>150900</v>
+        <v>151100</v>
       </c>
       <c r="G24" s="3">
-        <v>128400</v>
+        <v>128600</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1287,16 +1287,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>343400</v>
+        <v>343900</v>
       </c>
       <c r="E26" s="3">
-        <v>236100</v>
+        <v>236400</v>
       </c>
       <c r="F26" s="3">
-        <v>235500</v>
+        <v>235800</v>
       </c>
       <c r="G26" s="3">
-        <v>190900</v>
+        <v>191200</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1322,16 +1322,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>262200</v>
+        <v>262600</v>
       </c>
       <c r="E27" s="3">
-        <v>176200</v>
+        <v>176400</v>
       </c>
       <c r="F27" s="3">
-        <v>155000</v>
+        <v>155200</v>
       </c>
       <c r="G27" s="3">
-        <v>141300</v>
+        <v>141500</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1497,16 +1497,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>106500</v>
+        <v>106700</v>
       </c>
       <c r="E32" s="3">
-        <v>91200</v>
+        <v>91400</v>
       </c>
       <c r="F32" s="3">
-        <v>119900</v>
+        <v>120100</v>
       </c>
       <c r="G32" s="3">
-        <v>62200</v>
+        <v>62300</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>262200</v>
+        <v>262600</v>
       </c>
       <c r="E33" s="3">
-        <v>176200</v>
+        <v>176400</v>
       </c>
       <c r="F33" s="3">
-        <v>155000</v>
+        <v>155200</v>
       </c>
       <c r="G33" s="3">
-        <v>141300</v>
+        <v>141500</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1602,16 +1602,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>262200</v>
+        <v>262600</v>
       </c>
       <c r="E35" s="3">
-        <v>176200</v>
+        <v>176400</v>
       </c>
       <c r="F35" s="3">
-        <v>155000</v>
+        <v>155200</v>
       </c>
       <c r="G35" s="3">
-        <v>141300</v>
+        <v>141500</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1707,13 +1707,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3230100</v>
+        <v>3234600</v>
       </c>
       <c r="E41" s="3">
-        <v>3583400</v>
+        <v>3588500</v>
       </c>
       <c r="F41" s="3">
-        <v>3696800</v>
+        <v>3702000</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1742,13 +1742,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>336200</v>
+        <v>336600</v>
       </c>
       <c r="E42" s="3">
-        <v>92700</v>
+        <v>92900</v>
       </c>
       <c r="F42" s="3">
-        <v>264100</v>
+        <v>264500</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1777,13 +1777,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1575000</v>
+        <v>1577200</v>
       </c>
       <c r="E43" s="3">
-        <v>1635700</v>
+        <v>1638000</v>
       </c>
       <c r="F43" s="3">
-        <v>1587800</v>
+        <v>1590000</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1812,13 +1812,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4341900</v>
+        <v>4348000</v>
       </c>
       <c r="E44" s="3">
-        <v>4678000</v>
+        <v>4684600</v>
       </c>
       <c r="F44" s="3">
-        <v>5207400</v>
+        <v>5214700</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1847,13 +1847,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>142000</v>
+        <v>142200</v>
       </c>
       <c r="E45" s="3">
-        <v>170800</v>
+        <v>171100</v>
       </c>
       <c r="F45" s="3">
-        <v>1227700</v>
+        <v>1229400</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1882,13 +1882,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9625100</v>
+        <v>9638700</v>
       </c>
       <c r="E46" s="3">
-        <v>10160700</v>
+        <v>10175000</v>
       </c>
       <c r="F46" s="3">
-        <v>11983800</v>
+        <v>12000600</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1917,13 +1917,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5811300</v>
+        <v>5819500</v>
       </c>
       <c r="E47" s="3">
-        <v>5656800</v>
+        <v>5664700</v>
       </c>
       <c r="F47" s="3">
-        <v>5814200</v>
+        <v>5822400</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1952,13 +1952,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5601000</v>
+        <v>5608800</v>
       </c>
       <c r="E48" s="3">
-        <v>5207100</v>
+        <v>5214400</v>
       </c>
       <c r="F48" s="3">
-        <v>5199500</v>
+        <v>5206800</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1987,13 +1987,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1898100</v>
+        <v>1900800</v>
       </c>
       <c r="E49" s="3">
-        <v>1789700</v>
+        <v>1792200</v>
       </c>
       <c r="F49" s="3">
-        <v>1815800</v>
+        <v>1818400</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2092,7 +2092,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25300</v>
+        <v>25400</v>
       </c>
       <c r="E52" s="3">
         <v>22100</v>
@@ -2162,13 +2162,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22960900</v>
+        <v>22993100</v>
       </c>
       <c r="E54" s="3">
-        <v>22836300</v>
+        <v>22868400</v>
       </c>
       <c r="F54" s="3">
-        <v>24833200</v>
+        <v>24868100</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2227,13 +2227,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2440300</v>
+        <v>2443800</v>
       </c>
       <c r="E57" s="3">
-        <v>2182200</v>
+        <v>2185300</v>
       </c>
       <c r="F57" s="3">
-        <v>2496400</v>
+        <v>2499900</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2262,13 +2262,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1869600</v>
+        <v>1872200</v>
       </c>
       <c r="E58" s="3">
-        <v>2089000</v>
+        <v>2091900</v>
       </c>
       <c r="F58" s="3">
-        <v>2303400</v>
+        <v>2306700</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2297,13 +2297,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1762800</v>
+        <v>1765300</v>
       </c>
       <c r="E59" s="3">
-        <v>2464100</v>
+        <v>2467600</v>
       </c>
       <c r="F59" s="3">
-        <v>3574200</v>
+        <v>3579200</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2332,13 +2332,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6072700</v>
+        <v>6081300</v>
       </c>
       <c r="E60" s="3">
-        <v>6735300</v>
+        <v>6744800</v>
       </c>
       <c r="F60" s="3">
-        <v>8373900</v>
+        <v>8385700</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2367,13 +2367,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5663400</v>
+        <v>5671400</v>
       </c>
       <c r="E61" s="3">
-        <v>5294500</v>
+        <v>5302000</v>
       </c>
       <c r="F61" s="3">
-        <v>5244100</v>
+        <v>5251400</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1305900</v>
+        <v>1307800</v>
       </c>
       <c r="E62" s="3">
-        <v>1307800</v>
+        <v>1309600</v>
       </c>
       <c r="F62" s="3">
-        <v>1381700</v>
+        <v>1383700</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2542,13 +2542,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16993300</v>
+        <v>17017200</v>
       </c>
       <c r="E66" s="3">
-        <v>17131900</v>
+        <v>17156000</v>
       </c>
       <c r="F66" s="3">
-        <v>19003900</v>
+        <v>19030600</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2732,13 +2732,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4370600</v>
+        <v>4376700</v>
       </c>
       <c r="E72" s="3">
-        <v>4162700</v>
+        <v>4168500</v>
       </c>
       <c r="F72" s="3">
-        <v>4061700</v>
+        <v>4067500</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2872,13 +2872,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5967500</v>
+        <v>5975900</v>
       </c>
       <c r="E76" s="3">
-        <v>5704400</v>
+        <v>5712400</v>
       </c>
       <c r="F76" s="3">
-        <v>5829400</v>
+        <v>5837500</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2982,16 +2982,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>262200</v>
+        <v>262600</v>
       </c>
       <c r="E81" s="3">
-        <v>176200</v>
+        <v>176400</v>
       </c>
       <c r="F81" s="3">
-        <v>155000</v>
+        <v>155200</v>
       </c>
       <c r="G81" s="3">
-        <v>141300</v>
+        <v>141500</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -3242,16 +3242,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>326200</v>
+        <v>326600</v>
       </c>
       <c r="E89" s="3">
-        <v>231500</v>
-      </c>
-      <c r="F89" s="3">
-        <v>1099800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1032400</v>
+        <v>231800</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3298,7 +3298,7 @@
         <v>-157900</v>
       </c>
       <c r="F91" s="3">
-        <v>-50200</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-566100</v>
+        <v>-566900</v>
       </c>
       <c r="E94" s="3">
-        <v>49100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-425500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>32300</v>
+        <v>49200</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3447,16 +3447,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-61200</v>
+        <v>-61300</v>
       </c>
       <c r="E96" s="3">
-        <v>-66900</v>
+        <v>-67000</v>
       </c>
       <c r="F96" s="3">
-        <v>-91800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-41800</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -3587,16 +3587,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-194600</v>
+        <v>-194900</v>
       </c>
       <c r="E100" s="3">
-        <v>-233500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1263900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>679900</v>
+        <v>-233800</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3622,16 +3622,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>81100</v>
+        <v>81300</v>
       </c>
       <c r="E101" s="3">
-        <v>-160500</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-39900</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-238600</v>
+        <v>-160700</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3657,16 +3657,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-353400</v>
+        <v>-353900</v>
       </c>
       <c r="E102" s="3">
-        <v>-113400</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-629500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-558800</v>
+        <v>-113600</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="92">
   <si>
     <t>SGHIY</t>
   </si>
@@ -656,171 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>2552600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1640200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2068100</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>1951700</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>1460200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1092700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1430800</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>1431000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>1092500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>547500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>637400</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>520600</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -834,8 +884,12 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,8 +923,20 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -904,22 +970,34 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-32700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>31000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -930,8 +1008,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -939,31 +1017,43 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -974,8 +1064,20 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -986,78 +1088,106 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1700300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1172300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1560400</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>1568800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>852300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>467900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>507800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>382900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1071,183 +1201,247 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-106700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-91400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-120100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-62300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>742800</v>
-      </c>
-      <c r="E21" s="3">
-        <v>486400</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>409000</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>700</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>745000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>375800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>386900</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>319700</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>401100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>139300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>151100</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>128600</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1281,78 +1475,114 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>343900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>236400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>235800</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>191200</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>262600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>176400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>155200</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>141500</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1386,31 +1616,43 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1421,8 +1663,20 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1456,8 +1710,20 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1491,78 +1757,114 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>106700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>91400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>120100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>62300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>262600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>176400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>155200</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>141500</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1596,83 +1898,119 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>262600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>176400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>155200</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>141500</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1686,8 +2024,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1701,31 +2043,35 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3234600</v>
+        <v>2683200</v>
       </c>
       <c r="E41" s="3">
-        <v>3588500</v>
+        <v>2682500</v>
       </c>
       <c r="F41" s="3">
-        <v>3702000</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>3178900</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3171700</v>
+      </c>
+      <c r="H41" s="3">
+        <v>3229100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3221200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3571100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1736,31 +2082,43 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>336600</v>
+        <v>773300</v>
       </c>
       <c r="E42" s="3">
-        <v>92900</v>
+        <v>773100</v>
       </c>
       <c r="F42" s="3">
-        <v>264500</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>290900</v>
+      </c>
+      <c r="G42" s="3">
+        <v>290300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>336100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>335300</v>
+      </c>
+      <c r="J42" s="3">
+        <v>92400</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1771,31 +2129,43 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1577200</v>
+        <v>1552800</v>
       </c>
       <c r="E43" s="3">
-        <v>1638000</v>
+        <v>1552500</v>
       </c>
       <c r="F43" s="3">
-        <v>1590000</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>1658100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1654400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1482000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1478400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1594200</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1806,31 +2176,43 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4348000</v>
+        <v>3252100</v>
       </c>
       <c r="E44" s="3">
-        <v>4684600</v>
+        <v>3251300</v>
       </c>
       <c r="F44" s="3">
-        <v>5214700</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>4092200</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4083000</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4340600</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4330100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>4661900</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1841,31 +2223,43 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>142200</v>
+        <v>42000</v>
       </c>
       <c r="E45" s="3">
-        <v>171100</v>
+        <v>42000</v>
       </c>
       <c r="F45" s="3">
-        <v>1229400</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>24500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>24400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>54200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>54100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>60800</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1876,31 +2270,43 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9638700</v>
+        <v>8495700</v>
       </c>
       <c r="E46" s="3">
-        <v>10175000</v>
+        <v>8493500</v>
       </c>
       <c r="F46" s="3">
-        <v>12000600</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>9355800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>9334600</v>
+      </c>
+      <c r="H46" s="3">
+        <v>9622200</v>
+      </c>
+      <c r="I46" s="3">
+        <v>9598900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>10125700</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1911,31 +2317,43 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5819500</v>
+        <v>2790600</v>
       </c>
       <c r="E47" s="3">
-        <v>5664700</v>
+        <v>2789900</v>
       </c>
       <c r="F47" s="3">
-        <v>5822400</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>2594000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2588200</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2636200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2629900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2443300</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1946,31 +2364,43 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5608800</v>
+        <v>897700</v>
       </c>
       <c r="E48" s="3">
-        <v>5214400</v>
+        <v>897500</v>
       </c>
       <c r="F48" s="3">
-        <v>5206800</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>920200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>918100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>969400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>967100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>871900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1981,31 +2411,43 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900800</v>
+        <v>2111600</v>
       </c>
       <c r="E49" s="3">
-        <v>1792200</v>
+        <v>2111100</v>
       </c>
       <c r="F49" s="3">
-        <v>1818400</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>1819700</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1815600</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1897500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1892900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1783500</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2016,8 +2458,20 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2051,8 +2505,20 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,31 +2552,43 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25400</v>
+        <v>4473100</v>
       </c>
       <c r="E52" s="3">
-        <v>22100</v>
+        <v>4471900</v>
       </c>
       <c r="F52" s="3">
-        <v>19900</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>4614500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4604000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4629800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4618600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4317300</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2121,8 +2599,20 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2156,31 +2646,43 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22993100</v>
+        <v>21694600</v>
       </c>
       <c r="E54" s="3">
-        <v>22868400</v>
+        <v>21689100</v>
       </c>
       <c r="F54" s="3">
-        <v>24868100</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>22397600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>22347100</v>
+      </c>
+      <c r="H54" s="3">
+        <v>22953800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>22898200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>22757700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2191,8 +2693,20 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2206,8 +2720,12 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2221,31 +2739,35 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2443800</v>
+        <v>739300</v>
       </c>
       <c r="E57" s="3">
-        <v>2185300</v>
+        <v>739100</v>
       </c>
       <c r="F57" s="3">
-        <v>2499900</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>668900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>667400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>768600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>766700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>714700</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2256,31 +2778,43 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1872200</v>
+        <v>2479100</v>
       </c>
       <c r="E58" s="3">
-        <v>2091900</v>
+        <v>2478500</v>
       </c>
       <c r="F58" s="3">
-        <v>2306700</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>1745200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1741200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1869000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1864500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2081800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2291,31 +2825,43 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1765300</v>
+        <v>1739600</v>
       </c>
       <c r="E59" s="3">
-        <v>2467600</v>
+        <v>1739200</v>
       </c>
       <c r="F59" s="3">
-        <v>3579200</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>2940400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2933700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3136300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3128700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3900300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2326,31 +2872,43 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6081300</v>
+        <v>5171400</v>
       </c>
       <c r="E60" s="3">
-        <v>6744800</v>
+        <v>5170100</v>
       </c>
       <c r="F60" s="3">
-        <v>8385700</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>5369800</v>
+      </c>
+      <c r="G60" s="3">
+        <v>5357700</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6070900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6056200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>6712100</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2361,31 +2919,43 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5671400</v>
+        <v>5215300</v>
       </c>
       <c r="E61" s="3">
-        <v>5302000</v>
+        <v>5214000</v>
       </c>
       <c r="F61" s="3">
-        <v>5251400</v>
+        <v>5997800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>5984200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5661700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>5648000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>5276300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2396,31 +2966,43 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1307800</v>
+        <v>10100</v>
       </c>
       <c r="E62" s="3">
-        <v>1309600</v>
+        <v>10100</v>
       </c>
       <c r="F62" s="3">
-        <v>1383700</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>7900</v>
+      </c>
+      <c r="G62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>9800</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2431,8 +3013,20 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2466,8 +3060,20 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,8 +3107,20 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2536,31 +3154,43 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17017200</v>
+        <v>11615000</v>
       </c>
       <c r="E66" s="3">
-        <v>17156000</v>
+        <v>11612100</v>
       </c>
       <c r="F66" s="3">
-        <v>19030600</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>12615500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>12587000</v>
+      </c>
+      <c r="H66" s="3">
+        <v>13038100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>13006500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>13291700</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2571,8 +3201,20 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2586,8 +3228,12 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2621,8 +3267,20 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2656,8 +3314,20 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2691,8 +3361,20 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2726,31 +3408,43 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4376700</v>
+        <v>5484200</v>
       </c>
       <c r="E72" s="3">
-        <v>4168500</v>
+        <v>5482800</v>
       </c>
       <c r="F72" s="3">
-        <v>4067500</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>5307400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>5295400</v>
+      </c>
+      <c r="H72" s="3">
+        <v>5223600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>5210900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>5004100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2761,8 +3455,20 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2796,8 +3502,20 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2831,8 +3549,20 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2866,31 +3596,43 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5975900</v>
+        <v>6124300</v>
       </c>
       <c r="E76" s="3">
-        <v>5712400</v>
+        <v>6122800</v>
       </c>
       <c r="F76" s="3">
-        <v>5837500</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>5927000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>5913600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>5965700</v>
+      </c>
+      <c r="I76" s="3">
+        <v>5951200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>5684800</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2901,8 +3643,20 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2936,83 +3690,119 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>262600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>176400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>155200</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>141500</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3026,31 +3816,35 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>17900</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3061,8 +3855,20 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3096,8 +3902,20 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3131,8 +3949,20 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3166,8 +3996,20 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3201,8 +4043,20 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3236,31 +4090,43 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>326600</v>
+        <v>363800</v>
       </c>
       <c r="E89" s="3">
-        <v>231800</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>363700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>163000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>162600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>115300</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3271,8 +4137,20 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3286,31 +4164,35 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3262900</v>
+        <v>-14200</v>
       </c>
       <c r="E91" s="3">
-        <v>-157900</v>
+        <v>-14200</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-14900</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-74500</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-74400</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-10100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3321,8 +4203,20 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3356,8 +4250,20 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3391,31 +4297,43 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-566900</v>
+        <v>-477300</v>
       </c>
       <c r="E94" s="3">
-        <v>49200</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-477200</v>
+      </c>
+      <c r="F94" s="3">
+        <v>31900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>31800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-283000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-282300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>24500</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3426,8 +4344,20 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3441,31 +4371,35 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-61300</v>
+        <v>32800</v>
       </c>
       <c r="E96" s="3">
-        <v>-67000</v>
+        <v>32800</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>32800</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>30600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3476,8 +4410,20 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3511,8 +4457,20 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3546,8 +4504,20 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3581,31 +4551,43 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-194900</v>
+        <v>-130400</v>
       </c>
       <c r="E100" s="3">
-        <v>-233800</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-130300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>41300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>41200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-97300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-116400</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3616,31 +4598,43 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>81300</v>
+        <v>40600</v>
       </c>
       <c r="E101" s="3">
-        <v>-160700</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>40500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-79800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-118700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3651,31 +4645,43 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-353900</v>
+        <v>-256200</v>
       </c>
       <c r="E102" s="3">
-        <v>-113600</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-256100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-176600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-176200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-56500</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -3684,6 +4690,18 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
